--- a/古思特产品资料-2026.4.3.xlsx
+++ b/古思特产品资料-2026.4.3.xlsx
@@ -3584,14 +3584,6 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3623,6 +3615,14 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4570,10 +4570,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="33" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -4902,10 +4902,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5076,19 +5076,19 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5127,7 +5127,7 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5172,7 +5172,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5223,7 +5223,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -16201,7 +16201,7 @@
     <col min="7" max="7" width="30.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.2" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.4" style="1" customWidth="1"/>
-    <col min="10" max="10" width="46.7833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="59.2833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="86.2416666666667" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
